--- a/trunk/psse_validation/data/IEEE14bus.raw.xlsx
+++ b/trunk/psse_validation/data/IEEE14bus.raw.xlsx
@@ -16,21 +16,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
+  <si>
+    <t>names</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>Vm</t>
+  </si>
+  <si>
+    <t>Va(rad)</t>
+  </si>
   <si>
     <t>Va(deg)</t>
   </si>
   <si>
-    <t>Va(rad)</t>
-  </si>
-  <si>
-    <t>Vm</t>
-  </si>
-  <si>
-    <t>names</t>
-  </si>
-  <si>
-    <t>number</t>
+    <t>Vnom</t>
   </si>
   <si>
     <t xml:space="preserve">BUS 1       </t>
@@ -75,10 +78,25 @@
     <t xml:space="preserve">BUS 14      </t>
   </si>
   <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Q</t>
+    <t>Pf</t>
+  </si>
+  <si>
+    <t>Qf</t>
+  </si>
+  <si>
+    <t>Pt</t>
+  </si>
+  <si>
+    <t>Qt</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>ckt</t>
   </si>
   <si>
     <t>1_2_1</t>
@@ -496,10 +514,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -515,285 +533,330 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>0</v>
+      <c r="B2" t="s">
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1.05999994277954</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
+      <c r="E2">
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>-4.98259004842459</v>
+      <c r="B3" t="s">
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>-0.0869626016221127</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>1.04499994352525</v>
       </c>
-      <c r="E3" t="s">
-        <v>6</v>
+      <c r="E3">
+        <v>-0.0869626016221127</v>
       </c>
       <c r="F3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>-4.98259004842459</v>
+      </c>
+      <c r="G3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>-12.72510119424</v>
+      <c r="B4" t="s">
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>-0.222094913488951</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>1.01000002040611</v>
       </c>
-      <c r="E4" t="s">
-        <v>7</v>
+      <c r="E4">
+        <v>-0.222094913488951</v>
       </c>
       <c r="F4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>-12.72510119424</v>
+      </c>
+      <c r="G4">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>-10.3129016323451</v>
+      <c r="B5" t="s">
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>-0.17999408891872</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>1.0176708465552</v>
       </c>
-      <c r="E5" t="s">
-        <v>8</v>
+      <c r="E5">
+        <v>-0.17999408891872</v>
       </c>
       <c r="F5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>-10.3129016323451</v>
+      </c>
+      <c r="G5">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>-8.77385423698818</v>
+      <c r="B6" t="s">
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>-0.153132644525499</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>1.01951387726481</v>
       </c>
-      <c r="E6" t="s">
-        <v>9</v>
+      <c r="E6">
+        <v>-0.153132644525499</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>-8.77385423698818</v>
+      </c>
+      <c r="G6">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7">
-        <v>-14.220947583309</v>
+      <c r="B7" t="s">
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>-0.248202358082272</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>1.07000009494841</v>
       </c>
-      <c r="E7" t="s">
-        <v>10</v>
+      <c r="E7">
+        <v>-0.248202358082272</v>
       </c>
       <c r="F7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>-14.220947583309</v>
+      </c>
+      <c r="G7">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8">
-        <v>-13.3596292802441</v>
+      <c r="B8" t="s">
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>-0.2331695177861</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>1.06151949797749</v>
       </c>
-      <c r="E8" t="s">
-        <v>11</v>
+      <c r="E8">
+        <v>-0.2331695177861</v>
       </c>
       <c r="F8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>-13.3596292802441</v>
+      </c>
+      <c r="G8">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9">
-        <v>-13.359627680099</v>
+      <c r="B9" t="s">
+        <v>13</v>
       </c>
       <c r="C9">
-        <v>-0.2331694898583</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>1.09000004689213</v>
       </c>
-      <c r="E9" t="s">
-        <v>12</v>
+      <c r="E9">
+        <v>-0.2331694898583</v>
       </c>
       <c r="F9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>-13.359627680099</v>
+      </c>
+      <c r="G9">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10">
-        <v>-14.9385218594958</v>
+      <c r="B10" t="s">
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>-0.260726391829347</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>1.05593170275263</v>
       </c>
-      <c r="E10" t="s">
-        <v>13</v>
+      <c r="E10">
+        <v>-0.260726391829347</v>
       </c>
       <c r="F10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>-14.9385218594958</v>
+      </c>
+      <c r="G10">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11">
-        <v>-15.0972899076677</v>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>-0.263497417016912</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>1.05098461506576</v>
       </c>
-      <c r="E11" t="s">
-        <v>14</v>
+      <c r="E11">
+        <v>-0.263497417016912</v>
       </c>
       <c r="F11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>-15.0972899076677</v>
+      </c>
+      <c r="G11">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12">
-        <v>-14.7906234906042</v>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>-0.258145078333859</v>
+        <v>11</v>
       </c>
       <c r="D12">
         <v>1.0569065179562</v>
       </c>
-      <c r="E12" t="s">
-        <v>15</v>
+      <c r="E12">
+        <v>-0.258145078333859</v>
       </c>
       <c r="F12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>-14.7906234906042</v>
+      </c>
+      <c r="G12">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13">
-        <v>-15.0755859561088</v>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>-0.263118611601517</v>
+        <v>12</v>
       </c>
       <c r="D13">
         <v>1.05518858778003</v>
       </c>
-      <c r="E13" t="s">
-        <v>16</v>
+      <c r="E13">
+        <v>-0.263118611601517</v>
       </c>
       <c r="F13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>-15.0755859561088</v>
+      </c>
+      <c r="G13">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14">
-        <v>-15.1562782794617</v>
+      <c r="B14" t="s">
+        <v>18</v>
       </c>
       <c r="C14">
-        <v>-0.264526958325109</v>
+        <v>13</v>
       </c>
       <c r="D14">
         <v>1.05038174002869</v>
       </c>
-      <c r="E14" t="s">
-        <v>17</v>
+      <c r="E14">
+        <v>-0.264526958325109</v>
       </c>
       <c r="F14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>-15.1562782794617</v>
+      </c>
+      <c r="G14">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15">
-        <v>-16.033644302534</v>
+      <c r="B15" t="s">
+        <v>19</v>
       </c>
       <c r="C15">
-        <v>-0.279839884172848</v>
+        <v>14</v>
       </c>
       <c r="D15">
         <v>1.03552999636276</v>
       </c>
-      <c r="E15" t="s">
-        <v>18</v>
+      <c r="E15">
+        <v>-0.279839884172848</v>
       </c>
       <c r="F15">
-        <v>14</v>
+        <v>-16.033644302534</v>
+      </c>
+      <c r="G15">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -803,256 +866,526 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2">
         <v>156.882888793945</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>-20.404317855835</v>
       </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>-152.585287570953</v>
+      </c>
+      <c r="F2">
+        <v>33.5255298614502</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3">
         <v>75.5103759765625</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>3.85497808456421</v>
       </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>-72.7475032806396</v>
+      </c>
+      <c r="F3">
+        <v>7.55037260055542</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4">
         <v>73.2375793457031</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>3.56018662452698</v>
       </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>-70.9143102169037</v>
+      </c>
+      <c r="F4">
+        <v>6.22780203819275</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5">
         <v>56.1314926147461</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>-1.55035758018494</v>
       </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>-54.45483481884</v>
+      </c>
+      <c r="F5">
+        <v>6.63774943351746</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6">
         <v>41.5162162780762</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>1.17099213600159</v>
       </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>-40.6124628186226</v>
+      </c>
+      <c r="F6">
+        <v>1.58835196495056</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7">
         <v>-23.2856884002686</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>4.47312545776367</v>
       </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7">
+        <v>23.659133374691</v>
+      </c>
+      <c r="F7">
+        <v>-3.51997977495193</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8">
         <v>-61.1582221984863</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>15.8236522674561</v>
       </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8">
+        <v>61.6726416945457</v>
+      </c>
+      <c r="F8">
+        <v>-14.2010151147842</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9">
         <v>7.35327816009521</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>3.56048059463501</v>
       </c>
-      <c r="D9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9">
+        <v>-7.29790477082133</v>
+      </c>
+      <c r="F9">
+        <v>-3.44452180713415</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
+      </c>
+      <c r="H9">
+        <v>11</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10">
         <v>7.78606748580933</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>2.50341534614563</v>
       </c>
-      <c r="D10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10">
+        <v>-7.71425823122263</v>
+      </c>
+      <c r="F10">
+        <v>-2.3539602458477</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+      <c r="H10">
+        <v>12</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11">
         <v>17.7479782104492</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>7.21657943725586</v>
       </c>
-      <c r="D11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11">
+        <v>-17.5358927547932</v>
+      </c>
+      <c r="F11">
+        <v>-6.79891696572304</v>
+      </c>
+      <c r="G11">
+        <v>6</v>
+      </c>
+      <c r="H11">
+        <v>13</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12">
         <v>2.63677968348475e-14</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-17.1629867553711</v>
       </c>
-      <c r="D12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12">
+        <v>-2.63677968348475e-14</v>
+      </c>
+      <c r="F12">
+        <v>17.6234684586525</v>
+      </c>
+      <c r="G12">
+        <v>7</v>
+      </c>
+      <c r="H12">
+        <v>8</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13">
         <v>28.0741748809814</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>5.77868270874023</v>
       </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13">
+        <v>-28.0741748809814</v>
+      </c>
+      <c r="F13">
+        <v>-4.97661417722702</v>
+      </c>
+      <c r="G13">
+        <v>7</v>
+      </c>
+      <c r="H13">
+        <v>9</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14">
         <v>5.22755146026611</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>4.21913051605225</v>
       </c>
-      <c r="D14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14">
+        <v>-5.21467663161457</v>
+      </c>
+      <c r="F14">
+        <v>-4.18492985516787</v>
+      </c>
+      <c r="G14">
+        <v>9</v>
+      </c>
+      <c r="H14">
+        <v>10</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15">
         <v>9.42637920379639</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>3.61000156402588</v>
       </c>
-      <c r="D15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15">
+        <v>-9.31022519618273</v>
+      </c>
+      <c r="F15">
+        <v>-3.36292643845081</v>
+      </c>
+      <c r="G15">
+        <v>9</v>
+      </c>
+      <c r="H15">
+        <v>14</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16">
         <v>-3.78532409667969</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>-1.61507034301758</v>
       </c>
-      <c r="D16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16">
+        <v>3.79790540039539</v>
+      </c>
+      <c r="F16">
+        <v>1.6445217859</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16">
+        <v>11</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17">
         <v>1.61425840854645</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>0.753960192203522</v>
       </c>
-      <c r="D17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17">
+        <v>-1.60796014266089</v>
+      </c>
+      <c r="F17">
+        <v>-0.748261761385947</v>
+      </c>
+      <c r="G17">
+        <v>12</v>
+      </c>
+      <c r="H17">
+        <v>13</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18">
         <v>5.64385175704956</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>1.74717843532562</v>
       </c>
-      <c r="D18" t="s">
-        <v>37</v>
+      <c r="E18">
+        <v>-5.58977380767465</v>
+      </c>
+      <c r="F18">
+        <v>-1.6370736733079</v>
+      </c>
+      <c r="G18">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>14</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1062,60 +1395,120 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2">
         <v>28.0741748809814</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>-9.68107032775879</v>
       </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>-28.0741748809814</v>
+      </c>
+      <c r="F2">
+        <v>11.3842849731445</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3">
         <v>16.0797557830811</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>-0.427612245082855</v>
       </c>
-      <c r="D3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>-16.0797557830811</v>
+      </c>
+      <c r="F3">
+        <v>1.73232311010361</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4">
         <v>44.0873222351074</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>12.4706726074219</v>
       </c>
-      <c r="D4" t="s">
-        <v>40</v>
+      <c r="E4">
+        <v>-44.0873222351074</v>
+      </c>
+      <c r="F4">
+        <v>-8.04951143264771</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
